--- a/Mosoriot Data.xlsx
+++ b/Mosoriot Data.xlsx
@@ -14,7 +14,7 @@
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
     <author/>
-    <author>tc={1c5b53be-5b34-4c48-a219-ff22145cd063}</author>
+    <author>tc={b3d84df6-92be-4a5e-994e-f9ab353182c6}</author>
   </authors>
   <commentList>
     <comment authorId="0" ref="B19">
@@ -22,7 +22,7 @@
         <t xml:space="preserve">60</t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{1c5b53be-5b34-4c48-a219-ff22145cd063}" ref="B19">
+    <comment authorId="1" xr:uid="{b3d84df6-92be-4a5e-994e-f9ab353182c6}" ref="B19">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="35">
   <si>
     <t>Serial No</t>
   </si>
@@ -131,7 +131,16 @@
     <t>3,4</t>
   </si>
   <si>
+    <t>4,7</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6</t>
+  </si>
+  <si>
     <t>1,5</t>
+  </si>
+  <si>
+    <t>4,5</t>
   </si>
 </sst>
 </file>
@@ -190,7 +199,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Eliakim Chete" id="{f90f6fc4-2522-4e14-942c-6ad261a1833f}" providerId="google-sheets"/>
+  <x18tc:person displayName="Eliakim Chete" id="{d321b5e5-665b-4f55-b6d7-ea4aa4322d1a}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -390,7 +399,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="B19" dT="2026-03-23T19:02:30.00" personId="{f90f6fc4-2522-4e14-942c-6ad261a1833f}" id="{1c5b53be-5b34-4c48-a219-ff22145cd063}" done="0">
+  <x18tc:threadedComment ref="B19" dT="2026-03-23T19:02:30.00" personId="{d321b5e5-665b-4f55-b6d7-ea4aa4322d1a}" id="{b3d84df6-92be-4a5e-994e-f9ab353182c6}" done="0">
     <x18tc:text xml:space="preserve">60</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1401,11 +1410,143 @@
       <c r="A15" s="1">
         <v>14.0</v>
       </c>
+      <c r="B15" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="P15" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="R15" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="S15" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="T15" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="U15" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="V15" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="W15" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1">
         <v>15.0</v>
       </c>
+      <c r="B16" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N16" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="P16" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="R16" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="S16" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T16" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="U16" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="V16" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="W16" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1">
@@ -1482,6 +1623,72 @@
       <c r="A18" s="1">
         <v>17.0</v>
       </c>
+      <c r="B18" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="R18" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="S18" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="T18" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="U18" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="V18" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="W18" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1">
@@ -1558,46 +1765,640 @@
       <c r="A20" s="1">
         <v>19.0</v>
       </c>
+      <c r="B20" s="1">
+        <v>62.0</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H20" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I20" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="O20" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="P20" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="R20" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="S20" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="T20" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="U20" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="V20" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="W20" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1">
         <v>20.0</v>
       </c>
+      <c r="B21" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I21" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O21" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="P21" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="R21" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="S21" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="T21" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="U21" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="V21" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="W21" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1">
         <v>21.0</v>
       </c>
+      <c r="B22" s="1">
+        <v>61.0</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E22" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I22" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N22" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O22" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="P22" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="R22" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="S22" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="T22" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="U22" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="V22" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="W22" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1">
         <v>22.0</v>
       </c>
+      <c r="B23" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I23" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="L23" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N23" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O23" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="P23" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="R23" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="S23" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="T23" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="U23" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="V23" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="W23" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1">
         <v>23.0</v>
       </c>
+      <c r="B24" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H24" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I24" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L24" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N24" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O24" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="P24" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="R24" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="S24" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="T24" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="U24" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="V24" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="W24" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1">
         <v>24.0</v>
       </c>
+      <c r="B25" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E25" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I25" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N25" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O25" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="P25" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="R25" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="S25" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T25" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="U25" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="V25" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="W25" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1">
         <v>25.0</v>
       </c>
+      <c r="B26" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E26" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N26" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O26" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="P26" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="R26" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="S26" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="T26" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="U26" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="V26" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="W26" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1">
         <v>26.0</v>
       </c>
+      <c r="B27" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I27" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="N27" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="O27" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="P27" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="R27" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="S27" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T27" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="U27" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="V27" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="W27" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1">
         <v>27.0</v>
       </c>
+      <c r="B28" s="1">
+        <v>81.0</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E28" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I28" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="J28" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N28" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O28" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="P28" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="R28" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="S28" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="T28" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="U28" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="V28" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="W28" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1">
@@ -1740,9 +2541,6 @@
       <c r="W30" s="1">
         <v>1.0</v>
       </c>
-      <c r="X30" s="1">
-        <v>1.0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="1">
@@ -2048,7 +2846,7 @@
         <v>1.0</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H35" s="1">
         <v>1.0</v>
@@ -2245,70 +3043,639 @@
       <c r="A38" s="1">
         <v>37.0</v>
       </c>
+      <c r="B38" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D38" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H38" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K38" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L38" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O38" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="P38" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="R38" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="S38" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="T38" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="U38" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="V38" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="W38" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1">
         <v>38.0</v>
       </c>
+      <c r="B39" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E39" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I39" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J39" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K39" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="L39" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N39" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O39" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="P39" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="R39" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="S39" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="T39" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="U39" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="V39" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="W39" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1">
         <v>39.0</v>
       </c>
+      <c r="B40" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H40" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I40" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="J40" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K40" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="L40" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N40" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O40" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="R40" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="S40" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T40" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="U40" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="V40" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="W40" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1">
         <v>40.0</v>
       </c>
+      <c r="B41" s="1">
+        <v>61.0</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I41" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="J41" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K41" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="L41" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="N41" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="O41" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="P41" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="R41" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="S41" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T41" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="U41" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="V41" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="W41" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1">
         <v>41.0</v>
       </c>
+      <c r="B42" s="1">
+        <v>78.0</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F42" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I42" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="J42" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K42" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="L42" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N42" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O42" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="P42" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="R42" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="S42" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="T42" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="U42" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="V42" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="W42" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1">
         <v>42.0</v>
       </c>
+      <c r="B43" s="1">
+        <v>62.0</v>
+      </c>
+      <c r="C43" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E43" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F43" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I43" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="J43" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K43" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="L43" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N43" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O43" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="P43" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="R43" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="S43" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T43" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="U43" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="V43" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="W43" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1">
         <v>43.0</v>
       </c>
+      <c r="B44" s="1">
+        <v>81.0</v>
+      </c>
+      <c r="C44" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D44" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I44" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K44" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="L44" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N44" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O44" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="P44" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="R44" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="S44" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="T44" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="U44" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="V44" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="W44" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1">
         <v>44.0</v>
       </c>
+      <c r="B45" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="C45" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D45" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I45" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J45" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K45" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="L45" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N45" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O45" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="P45" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="R45" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="S45" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="T45" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="U45" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="V45" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="W45" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1">
         <v>45.0</v>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1">
-        <v>46.0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1">
-        <v>47.0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1">
-        <v>48.0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1">
-        <v>49.0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1">
-        <v>50.0</v>
+      <c r="B46" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="C46" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E46" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F46" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I46" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K46" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="L46" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N46" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O46" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="P46" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="R46" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="S46" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="T46" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="U46" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="V46" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="W46" s="1">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>

--- a/Mosoriot Data.xlsx
+++ b/Mosoriot Data.xlsx
@@ -14,7 +14,7 @@
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
     <author/>
-    <author>tc={b3d84df6-92be-4a5e-994e-f9ab353182c6}</author>
+    <author>tc={6ec15924-1d50-4caf-9815-494420bdb5b5}</author>
   </authors>
   <commentList>
     <comment authorId="0" ref="B19">
@@ -22,7 +22,7 @@
         <t xml:space="preserve">60</t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{b3d84df6-92be-4a5e-994e-f9ab353182c6}" ref="B19">
+    <comment authorId="1" xr:uid="{6ec15924-1d50-4caf-9815-494420bdb5b5}" ref="B19">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="36">
   <si>
     <t>Serial No</t>
   </si>
@@ -142,6 +142,9 @@
   <si>
     <t>4,5</t>
   </si>
+  <si>
+    <t>2,4</t>
+  </si>
 </sst>
 </file>
 
@@ -199,7 +202,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Eliakim Chete" id="{d321b5e5-665b-4f55-b6d7-ea4aa4322d1a}" providerId="google-sheets"/>
+  <x18tc:person displayName="Eliakim Chete" id="{303fcfd3-275b-422c-bce3-ef4d9875873b}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -399,7 +402,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="B19" dT="2026-03-23T19:02:30.00" personId="{d321b5e5-665b-4f55-b6d7-ea4aa4322d1a}" id="{b3d84df6-92be-4a5e-994e-f9ab353182c6}" done="0">
+  <x18tc:threadedComment ref="B19" dT="2026-03-23T19:02:30.00" personId="{303fcfd3-275b-422c-bce3-ef4d9875873b}" id="{6ec15924-1d50-4caf-9815-494420bdb5b5}" done="0">
     <x18tc:text xml:space="preserve">60</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -3678,6 +3681,361 @@
         <v>1.0</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="B47" s="1">
+        <v>66.0</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D47" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E47" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="F47" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H47" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I47" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="J47" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="L47" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N47" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="O47" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="P47" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="R47" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="S47" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T47" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="U47" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="V47" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="W47" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="B48" s="1">
+        <v>78.0</v>
+      </c>
+      <c r="C48" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D48" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E48" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F48" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H48" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I48" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K48" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="L48" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M48" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="N48" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O48" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="P48" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="R48" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="S48" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T48" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="U48" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="V48" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="W48" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="B49" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="C49" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D49" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E49" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F49" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I49" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="J49" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="K49" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="L49" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M49" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="N49" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="O49" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="P49" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="Q49" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="R49" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="S49" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="T49" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="U49" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="V49" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="W49" s="1">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="B50" s="1">
+        <v>82.0</v>
+      </c>
+      <c r="C50" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D50" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E50" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="F50" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="I50" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="J50" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K50" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="L50" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N50" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O50" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="P50" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="R50" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="S50" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="T50" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="U50" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="V50" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="W50" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="B51" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="C51" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D51" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="E51" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="F51" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H51" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="I51" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="J51" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="K51" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="L51" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="O51" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="P51" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="Q51" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="R51" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="S51" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="T51" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="U51" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="V51" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="W51" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId4"/>
   <legacyDrawing r:id="rId5"/>
